--- a/Configs/GameConfig/Datas/BattleConfig.xlsx
+++ b/Configs/GameConfig/Datas/BattleConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +512,51 @@
           <t>LvDamageCoef</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>LvMissCap_HeroDef</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>LvMissCap_MonsterDef</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>LvCritCap</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>LvLuckyCap</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>LvDamageCapLv_HeroDef</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>LvDamageCapLv_MonsterDef</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>KnockbackScaleX_HeroDef</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>KnockbackScaleX_MonsterDef</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>KnockbackScaleY</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -616,6 +661,51 @@
           <t>float</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -720,6 +810,51 @@
           <t>等级压制-每级伤害系数</t>
         </is>
       </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>等级压制-英雄防守闪避系数封顶</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>等级压制-怪物防守闪避系数封顶</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>等级压制-暴击系数封顶(人怪两侧一致)</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>等级压制-幸运系数封顶(人怪两侧一致)</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>等级压制-英雄防守时伤害最多按几级算</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>等级压制-怪物防守时伤害最多按几级算</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>英雄被击退横向换算: px/s = Knockback.X × 本值</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>怪物被击退横向换算: px/s = Knockback.X × 本值</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>击退纵向换算: px/s = Knockback.Y × 本值(人怪一致)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
@@ -779,6 +914,33 @@
       </c>
       <c r="S6" t="n">
         <v>0.05</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/BattleConfig.xlsx
+++ b/Configs/GameConfig/Datas/BattleConfig.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Configs/GameConfig/Datas/BattleConfig.xlsx
+++ b/Configs/GameConfig/Datas/BattleConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB6"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,6 +557,11 @@
           <t>KnockbackScaleY</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>WsMax</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -706,6 +711,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -855,6 +865,11 @@
           <t>击退纵向换算: px/s = Knockback.Y × 本值(人怪一致)</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>无双值上限(旧项目满值 100;M6 供 HUD 无双条满值)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
@@ -941,6 +956,9 @@
       </c>
       <c r="AB6" t="n">
         <v>15</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/BattleConfig.xlsx
+++ b/Configs/GameConfig/Datas/BattleConfig.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -867,7 +867,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>无双值上限(旧项目满值 100;M6 供 HUD 无双条满值)</t>
+          <t>无双值上限(旧项目 BaseRoleProperies.gd:20)</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/BattleConfig.xlsx
+++ b/Configs/GameConfig/Datas/BattleConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,6 +562,16 @@
           <t>WsMax</t>
         </is>
       </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>DeathRestartDelay</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>ClearRestartDelay</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -716,6 +726,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -870,6 +890,16 @@
           <t>无双值上限(旧项目 BaseRoleProperies.gd:20)</t>
         </is>
       </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>英雄死亡后自动重开本关的等待秒数(含死亡动画 1.1 秒)</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>通关后自动重开本关的等待秒数(暂无结算界面时使用)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
@@ -959,6 +989,12 @@
       </c>
       <c r="AC6" t="n">
         <v>100</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/BattleConfig.xlsx
+++ b/Configs/GameConfig/Datas/BattleConfig.xlsx
@@ -1767,7 +1767,7 @@
       </c>
       <c r="AE5" s="0" t="inlineStr">
         <is>
-          <t>小怪受伤血条淡出秒数（官方 BaseMonster.showHpSlip 为 2 秒）</t>
+          <t>小怪受伤血条淡出总时长（秒）；本项目延长为4秒，官方原值2秒</t>
         </is>
       </c>
       <c r="AF5" s="1" t="inlineStr">
@@ -1879,7 +1879,7 @@
         <v>2.5</v>
       </c>
       <c r="AE6" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF6" s="0" t="n">
         <v>12.5</v>

--- a/Configs/GameConfig/Datas/BattleConfig.xlsx
+++ b/Configs/GameConfig/Datas/BattleConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3d3612e9fb534386"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd7cd78407d2f4b07"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1177,160 +1177,98 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##var</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">NameCn</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Desc</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DefK_Hero</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MdefK_Hero</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MissK_Hero</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DefK_Monster</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MdefK_Monster</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MissK_Monster</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CritK</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LuckyK_HeroAtk</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LuckyK_MonsterAtk</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CritBase</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LvMissCoef_HeroDef</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LvCritCoef_HeroDef</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LvMissCoef_MonsterDef</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LvCritCoef_MonsterDef</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LvLuckyCoef</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="S1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LvDamageCoef</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LvMissCap_HeroDef</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="U1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LvMissCap_MonsterDef</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LvCritCap</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="W1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LvLuckyCap</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="X1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LvDamageCapLv_HeroDef</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Y1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LvDamageCapLv_MonsterDef</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Z1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">KnockbackScaleX_HeroDef</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AA1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">KnockbackScaleX_MonsterDef</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AB1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">KnockbackScaleY</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AC1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">WsMax</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AD1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DeathRestartDelay</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AE1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MonsterHealthBarFadeDuration</x:t>
-        </x:is>
+      <x:c r="A1" t="str">
+        <x:v>##var</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>NameCn</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>Desc</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>DefK_Hero</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
+        <x:v>MdefK_Hero</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
+        <x:v>MissK_Hero</x:v>
+      </x:c>
+      <x:c r="G1" t="str">
+        <x:v>DefK_Monster</x:v>
+      </x:c>
+      <x:c r="H1" t="str">
+        <x:v>MdefK_Monster</x:v>
+      </x:c>
+      <x:c r="I1" t="str">
+        <x:v>MissK_Monster</x:v>
+      </x:c>
+      <x:c r="J1" t="str">
+        <x:v>CritK</x:v>
+      </x:c>
+      <x:c r="K1" t="str">
+        <x:v>LuckyK_HeroAtk</x:v>
+      </x:c>
+      <x:c r="L1" t="str">
+        <x:v>LuckyK_MonsterAtk</x:v>
+      </x:c>
+      <x:c r="M1" t="str">
+        <x:v>CritBase</x:v>
+      </x:c>
+      <x:c r="N1" t="str">
+        <x:v>LvMissCoef_HeroDef</x:v>
+      </x:c>
+      <x:c r="O1" t="str">
+        <x:v>LvCritCoef_HeroDef</x:v>
+      </x:c>
+      <x:c r="P1" t="str">
+        <x:v>LvMissCoef_MonsterDef</x:v>
+      </x:c>
+      <x:c r="Q1" t="str">
+        <x:v>LvCritCoef_MonsterDef</x:v>
+      </x:c>
+      <x:c r="R1" t="str">
+        <x:v>LvLuckyCoef</x:v>
+      </x:c>
+      <x:c r="S1" t="str">
+        <x:v>LvDamageCoef</x:v>
+      </x:c>
+      <x:c r="T1" t="str">
+        <x:v>LvMissCap_HeroDef</x:v>
+      </x:c>
+      <x:c r="U1" t="str">
+        <x:v>LvMissCap_MonsterDef</x:v>
+      </x:c>
+      <x:c r="V1" t="str">
+        <x:v>LvCritCap</x:v>
+      </x:c>
+      <x:c r="W1" t="str">
+        <x:v>LvLuckyCap</x:v>
+      </x:c>
+      <x:c r="X1" t="str">
+        <x:v>LvDamageCapLv_HeroDef</x:v>
+      </x:c>
+      <x:c r="Y1" t="str">
+        <x:v>LvDamageCapLv_MonsterDef</x:v>
+      </x:c>
+      <x:c r="Z1" t="str">
+        <x:v>KnockbackScaleX_HeroDef</x:v>
+      </x:c>
+      <x:c r="AA1" t="str">
+        <x:v>KnockbackScaleX_MonsterDef</x:v>
+      </x:c>
+      <x:c r="AB1" t="str">
+        <x:v>KnockbackScaleY</x:v>
+      </x:c>
+      <x:c r="AC1" t="str">
+        <x:v>WsMax</x:v>
+      </x:c>
+      <x:c r="AD1" t="str">
+        <x:v>DeathSettlementDelay</x:v>
+      </x:c>
+      <x:c r="AE1" t="str">
+        <x:v>MonsterHealthBarFadeDuration</x:v>
       </x:c>
       <x:c r="AF1" s="5" t="str">
         <x:v>WsGainPerDamageRatio</x:v>
@@ -1358,11 +1296,39 @@
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##var</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A2" t="str">
+        <x:v>##var</x:v>
+      </x:c>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
+      <x:c r="M2"/>
+      <x:c r="N2"/>
+      <x:c r="O2"/>
+      <x:c r="P2"/>
+      <x:c r="Q2"/>
+      <x:c r="R2"/>
+      <x:c r="S2"/>
+      <x:c r="T2"/>
+      <x:c r="U2"/>
+      <x:c r="V2"/>
+      <x:c r="W2"/>
+      <x:c r="X2"/>
+      <x:c r="Y2"/>
+      <x:c r="Z2"/>
+      <x:c r="AA2"/>
+      <x:c r="AB2"/>
+      <x:c r="AC2"/>
+      <x:c r="AD2"/>
+      <x:c r="AE2"/>
       <x:c r="AF2" s="5"/>
       <x:c r="AG2" s="5"/>
       <x:c r="AH2" s="5"/>
@@ -1373,160 +1339,98 @@
       <x:c r="AM2" s="5"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##type</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">string</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">string</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="S3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="U3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="W3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="X3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Y3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Z3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AA3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AB3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AC3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AD3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AE3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
+      <x:c r="A3" t="str">
+        <x:v>##type</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="J3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="K3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="L3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="M3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="N3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="O3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="P3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="Q3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="R3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="S3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="T3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="U3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="V3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="W3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="X3" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="Y3" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="Z3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AA3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AB3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AC3" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="AD3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AE3" t="str">
+        <x:v>float</x:v>
       </x:c>
       <x:c r="AF3" s="5" t="str">
         <x:v>float</x:v>
@@ -1554,11 +1458,39 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##group</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A4" t="str">
+        <x:v>##group</x:v>
+      </x:c>
+      <x:c r="B4"/>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
+      <x:c r="M4"/>
+      <x:c r="N4"/>
+      <x:c r="O4"/>
+      <x:c r="P4"/>
+      <x:c r="Q4"/>
+      <x:c r="R4"/>
+      <x:c r="S4"/>
+      <x:c r="T4"/>
+      <x:c r="U4"/>
+      <x:c r="V4"/>
+      <x:c r="W4"/>
+      <x:c r="X4"/>
+      <x:c r="Y4"/>
+      <x:c r="Z4"/>
+      <x:c r="AA4"/>
+      <x:c r="AB4"/>
+      <x:c r="AC4"/>
+      <x:c r="AD4"/>
+      <x:c r="AE4"/>
       <x:c r="AF4" s="5"/>
       <x:c r="AG4" s="5"/>
       <x:c r="AH4" s="5"/>
@@ -1569,160 +1501,98 @@
       <x:c r="AM4" s="5"/>
     </x:row>
     <x:row r="5" s="2" customFormat="1" ht="48" customHeight="1">
-      <x:c r="A5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">中文名</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">描述</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">英雄作防守方时物防减伤K: x/(x+K)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">英雄作防守方时魔防减伤K</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">英雄作防守方时被命中K: Miss/(Miss+K)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">怪物作防守方时物防减伤K</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">怪物作防守方时魔防减伤K</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">怪物作防守方时被命中K</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">暴击率基数: Crit/(Crit+K)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">英雄攻击时暴击倍率幸运K</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">怪物攻击时暴击倍率幸运K</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">暴击倍率基数: CritBase + Lucky/(Lucky+K)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">等级压制-英雄防守闪避系数</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">等级压制-英雄防守暴击系数</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">等级压制-怪物防守闪避系数</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">等级压制-怪物防守暴击系数</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">等级压制-幸运系数</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="S5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">等级压制-每级伤害系数</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">等级压制-英雄防守闪避系数封顶</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="U5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">等级压制-怪物防守闪避系数封顶</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">等级压制-暴击系数封顶(人怪两侧一致)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="W5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">等级压制-幸运系数封顶(人怪两侧一致)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="X5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">等级压制-英雄防守时伤害最多按几级算</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Y5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">等级压制-怪物防守时伤害最多按几级算</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Z5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">英雄被击退横向换算: px/s = Knockback.X × 本值</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AA5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">怪物被击退横向换算: px/s = Knockback.X × 本值</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AB5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">击退纵向换算: px/s = Knockback.Y × 本值(人怪一致)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AC5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">无双值上限(旧项目 BaseRoleProperies.gd:20)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AD5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">英雄死亡后自动重开本关的等待秒数(含死亡动画 1.1 秒)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AE5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">小怪受伤血条淡出总时长（秒）；本项目延长为4秒，官方原值2秒</x:t>
-        </x:is>
+      <x:c r="A5" t="str">
+        <x:v>##</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>中文名</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>描述</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>英雄作防守方时物防减伤K: x/(x+K)</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>英雄作防守方时魔防减伤K</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>英雄作防守方时被命中K: Miss/(Miss+K)</x:v>
+      </x:c>
+      <x:c r="G5" t="str">
+        <x:v>怪物作防守方时物防减伤K</x:v>
+      </x:c>
+      <x:c r="H5" t="str">
+        <x:v>怪物作防守方时魔防减伤K</x:v>
+      </x:c>
+      <x:c r="I5" t="str">
+        <x:v>怪物作防守方时被命中K</x:v>
+      </x:c>
+      <x:c r="J5" t="str">
+        <x:v>暴击率基数: Crit/(Crit+K)</x:v>
+      </x:c>
+      <x:c r="K5" t="str">
+        <x:v>英雄攻击时暴击倍率幸运K</x:v>
+      </x:c>
+      <x:c r="L5" t="str">
+        <x:v>怪物攻击时暴击倍率幸运K</x:v>
+      </x:c>
+      <x:c r="M5" t="str">
+        <x:v>暴击倍率基数: CritBase + Lucky/(Lucky+K)</x:v>
+      </x:c>
+      <x:c r="N5" t="str">
+        <x:v>等级压制-英雄防守闪避系数</x:v>
+      </x:c>
+      <x:c r="O5" t="str">
+        <x:v>等级压制-英雄防守暴击系数</x:v>
+      </x:c>
+      <x:c r="P5" t="str">
+        <x:v>等级压制-怪物防守闪避系数</x:v>
+      </x:c>
+      <x:c r="Q5" t="str">
+        <x:v>等级压制-怪物防守暴击系数</x:v>
+      </x:c>
+      <x:c r="R5" t="str">
+        <x:v>等级压制-幸运系数</x:v>
+      </x:c>
+      <x:c r="S5" t="str">
+        <x:v>等级压制-每级伤害系数</x:v>
+      </x:c>
+      <x:c r="T5" t="str">
+        <x:v>等级压制-英雄防守闪避系数封顶</x:v>
+      </x:c>
+      <x:c r="U5" t="str">
+        <x:v>等级压制-怪物防守闪避系数封顶</x:v>
+      </x:c>
+      <x:c r="V5" t="str">
+        <x:v>等级压制-暴击系数封顶(人怪两侧一致)</x:v>
+      </x:c>
+      <x:c r="W5" t="str">
+        <x:v>等级压制-幸运系数封顶(人怪两侧一致)</x:v>
+      </x:c>
+      <x:c r="X5" t="str">
+        <x:v>等级压制-英雄防守时伤害最多按几级算</x:v>
+      </x:c>
+      <x:c r="Y5" t="str">
+        <x:v>等级压制-怪物防守时伤害最多按几级算</x:v>
+      </x:c>
+      <x:c r="Z5" t="str">
+        <x:v>英雄被击退横向换算: px/s = Knockback.X × 本值</x:v>
+      </x:c>
+      <x:c r="AA5" t="str">
+        <x:v>怪物被击退横向换算: px/s = Knockback.X × 本值</x:v>
+      </x:c>
+      <x:c r="AB5" t="str">
+        <x:v>击退纵向换算: px/s = Knockback.Y × 本值(人怪一致)</x:v>
+      </x:c>
+      <x:c r="AC5" t="str">
+        <x:v>无双值上限(旧项目 BaseRoleProperies.gd:20)</x:v>
+      </x:c>
+      <x:c r="AD5" t="str">
+        <x:v>死亡动画播放后显示失败结算（秒）</x:v>
+      </x:c>
+      <x:c r="AE5" t="str">
+        <x:v>小怪受伤血条淡出总时长（秒）；本项目延长为4秒，官方原值2秒</x:v>
       </x:c>
       <x:c r="AF5" s="5" t="str">
         <x:v>命中蓄力：伤害/基础攻击×系数；不改变攻击力</x:v>
@@ -1750,15 +1620,12 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="B6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">战斗常数</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">沿用旧项目人怪两侧不一致的基数,集中在此处</x:t>
-        </x:is>
+      <x:c r="A6"/>
+      <x:c r="B6" t="str">
+        <x:v>战斗常数</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>沿用旧项目人怪两侧不一致的基数,集中在此处</x:v>
       </x:c>
       <x:c r="D6" t="n">
         <x:v>250</x:v>
@@ -1794,7 +1661,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="O6" t="n">
-        <x:v>0.07000000000000001</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="P6" t="n">
         <x:v>0.04</x:v>
@@ -1803,7 +1670,7 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="R6" t="n">
-        <x:v>0.07000000000000001</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="S6" t="n">
         <x:v>0.05</x:v>
